--- a/output/pdf_financials_xlsx/FNDX.xlsx
+++ b/output/pdf_financials_xlsx/FNDX.xlsx
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.535764</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.337862</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.15716</v>
       </c>
     </row>
     <row r="93">
@@ -3077,7 +3077,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3537,7 +3541,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.535764</v>
       </c>

--- a/output/pdf_financials_xlsx/FNDX.xlsx
+++ b/output/pdf_financials_xlsx/FNDX.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.035353</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.012717</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.663213</v>
+        <v>-3.698566</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.627121</v>
+        <v>-4.639838</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.663213</v>
+        <v>-3.698566</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.627121</v>
+        <v>-4.639838</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>0.043926</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.051594</v>
       </c>
     </row>
     <row r="35">
@@ -1062,7 +1062,7 @@
         <v>0.043926</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.051594</v>
       </c>
     </row>
     <row r="37">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">

--- a/output/pdf_financials_xlsx/FNDX.xlsx
+++ b/output/pdf_financials_xlsx/FNDX.xlsx
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>4.046864</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>2.77668</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.698078</v>
       </c>
     </row>
     <row r="121">
@@ -4033,7 +4033,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>4.046864</v>
       </c>

--- a/output/pdf_financials_xlsx/FNDX.xlsx
+++ b/output/pdf_financials_xlsx/FNDX.xlsx
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2.276427</v>
+        <v>2.330824</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.601787</v>
+        <v>2.656787</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -5977,7 +5977,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>0.054397</v>
       </c>
